--- a/excel/questcfg.xlsx
+++ b/excel/questcfg.xlsx
@@ -183,7 +183,8 @@
   </si>
   <si>
     <t>任务条件
-格式: 条件id_参数</t>
+格式:
+条件id_参数值_可选参数数组</t>
   </si>
   <si>
     <t xml:space="preserve">任务进度,格式:
@@ -523,12 +524,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1622,7 +1623,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" ht="40.5" spans="1:13">
+    <row r="3" ht="54" spans="1:13">
       <c r="A3" t="s">
         <v>14</v>
       </c>
